--- a/Mindful_Diabetes_Free_Guides/00_README_FIRST/Project_Manifest.xlsx
+++ b/Mindful_Diabetes_Free_Guides/00_README_FIRST/Project_Manifest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,22 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Topics</t>
+          <t>Print PDF</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Pages</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Web size KB</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Print size KB</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Medical Review</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Next Review</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
         </is>
       </c>
     </row>
@@ -481,22 +501,36 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nutrition, Blood sugar, Meal planning</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t>mindful-diabetes-mindful-plate-guide-2026-print.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>306</v>
+      </c>
+      <c r="H2" t="n">
+        <v>306</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2027-07-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Selectable text/bookmarks/links included; PDF/UA tagging pending</t>
         </is>
       </c>
     </row>
@@ -523,22 +557,36 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dietary fats, Heart health, Food swaps</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>mindful-diabetes-fats-without-fear-2026-print.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>301</v>
+      </c>
+      <c r="H3" t="n">
+        <v>301</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2027-07-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Selectable text/bookmarks/links included; PDF/UA tagging pending</t>
         </is>
       </c>
     </row>
@@ -565,22 +613,36 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grocery shopping, Food labels, Budget meals</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>mindful-diabetes-grocery-store-guide-2026-print.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>302</v>
+      </c>
+      <c r="H4" t="n">
+        <v>302</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2027-07-30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Selectable text/bookmarks/links included; PDF/UA tagging pending</t>
         </is>
       </c>
     </row>
@@ -607,22 +669,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Habits, Prevention, Trackers</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>mindful-diabetes-7-day-prevention-reset-2026-print.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G5" t="n">
+        <v>312</v>
+      </c>
+      <c r="H5" t="n">
+        <v>312</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2027-07-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Selectable text/bookmarks/links included; PDF/UA tagging pending</t>
         </is>
       </c>
     </row>
@@ -649,22 +725,36 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brain health, Diabetes, Prevention</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>mindful-diabetes-blood-sugar-brain-health-2026-print.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G6" t="n">
+        <v>306</v>
+      </c>
+      <c r="H6" t="n">
+        <v>306</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2027-07-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Selectable text/bookmarks/links included; PDF/UA tagging pending</t>
         </is>
       </c>
     </row>
